--- a/OMOP Analysis/Results/Output_overall_healthcare_roles-OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_overall_healthcare_roles-OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,27 +375,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2">
-        <v>1732238</v>
+        <v>397191</v>
       </c>
       <c r="C2">
-        <v>45.38</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B3">
-        <v>1028274</v>
+        <v>350318</v>
       </c>
       <c r="C3">
-        <v>26.94</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="4">
@@ -405,10 +405,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>431420</v>
+        <v>42557</v>
       </c>
       <c r="C4">
-        <v>11.3</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="5">
@@ -418,10 +418,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>537188</v>
+        <v>67002</v>
       </c>
       <c r="C5">
-        <v>14.07</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="6">
@@ -431,18 +431,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>87733</v>
+        <v>31006</v>
       </c>
       <c r="C6">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7">
-        <v>102</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
+        <v>3.49</v>
       </c>
     </row>
   </sheetData>
@@ -452,7 +444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -480,145 +472,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Case Manager / Care Coordinator</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="C2">
-        <v>487622</v>
+        <v>42901</v>
       </c>
       <c r="D2">
-        <v>12.77515716061625</v>
+        <v>4.830791127766379</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Health Information Technician</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="C3">
-        <v>75271</v>
+        <v>325922</v>
       </c>
       <c r="D3">
-        <v>1.972016961164069</v>
+        <v>36.6998696054608</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other Technician</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="C4">
-        <v>831207</v>
+        <v>28368</v>
       </c>
       <c r="D4">
-        <v>21.77670420531549</v>
+        <v>3.194328400561214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Physician Office Based Coding Specialist</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="C5">
-        <v>11740</v>
+        <v>350318</v>
       </c>
       <c r="D5">
-        <v>0.3075750172585215</v>
+        <v>39.44693798039353</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Registered Record Administrator</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="C6">
-        <v>325580</v>
+        <v>11862</v>
       </c>
       <c r="D6">
-        <v>8.529835955624312</v>
+        <v>1.335699502518934</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="C7">
-        <v>818</v>
+        <v>90</v>
       </c>
       <c r="D7">
-        <v>0.02143069541034673</v>
+        <v>0.01013429061091756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="C8">
-        <v>909484</v>
+        <v>1916</v>
       </c>
       <c r="D8">
-        <v>23.82747504227846</v>
+        <v>0.2157477867835338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="C9">
-        <v>118790</v>
+        <v>15197</v>
       </c>
       <c r="D9">
-        <v>3.112166635446318</v>
+        <v>1.711231271267935</v>
       </c>
     </row>
     <row r="10">
@@ -629,14 +621,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="C10">
-        <v>50618</v>
+        <v>3848</v>
       </c>
       <c r="D10">
-        <v>1.326135623815319</v>
+        <v>0.4332972252312307</v>
       </c>
     </row>
     <row r="11">
@@ -647,104 +639,104 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="C11">
-        <v>212202</v>
+        <v>9644</v>
       </c>
       <c r="D11">
-        <v>5.559457735288993</v>
+        <v>1.085945540574321</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>Behavioral Health &amp; Social Service Providers, Psychologist, Clinical</t>
         </is>
       </c>
       <c r="C12">
-        <v>383</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>0.01003417645741173</v>
+        <v>0.0009008258320815607</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="C13">
-        <v>9972</v>
+        <v>22347</v>
       </c>
       <c r="D13">
-        <v>0.2612553724107305</v>
+        <v>2.51634435869083</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="C14">
-        <v>72305</v>
+        <v>51</v>
       </c>
       <c r="D14">
-        <v>1.894311041130954</v>
+        <v>0.00574276467951995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="C15">
-        <v>37632</v>
+        <v>36677</v>
       </c>
       <c r="D15">
-        <v>0.9859167844525283</v>
+        <v>4.129948630406926</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="C16">
-        <v>48308</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>1.265616178341112</v>
+        <v>0.0003378096870305853</v>
       </c>
     </row>
     <row r="17">
@@ -755,14 +747,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Behavioral Health &amp; Social Service Providers, Psychologist, Clinical</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>426</v>
       </c>
       <c r="D17">
-        <v>0.0002881878355914597</v>
+        <v>0.04796897555834311</v>
       </c>
     </row>
     <row r="18">
@@ -773,14 +765,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="C18">
-        <v>118532</v>
+        <v>6094</v>
       </c>
       <c r="D18">
-        <v>3.105407320756991</v>
+        <v>0.686204077588129</v>
       </c>
     </row>
     <row r="19">
@@ -791,14 +783,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="C19">
-        <v>132</v>
+        <v>468</v>
       </c>
       <c r="D19">
-        <v>0.003458254027097516</v>
+        <v>0.0526983111767713</v>
       </c>
     </row>
     <row r="20">
@@ -809,14 +801,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="C20">
-        <v>120759</v>
+        <v>112</v>
       </c>
       <c r="D20">
-        <v>3.163752258017189</v>
+        <v>0.01261156164914185</v>
       </c>
     </row>
     <row r="21">
@@ -827,14 +819,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="D21">
-        <v>0.0001047955765787126</v>
+        <v>0.01587705529043751</v>
       </c>
     </row>
     <row r="22">
@@ -845,14 +837,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="C22">
-        <v>2150</v>
+        <v>75</v>
       </c>
       <c r="D22">
-        <v>0.05632762241105803</v>
+        <v>0.008445242175764632</v>
       </c>
     </row>
     <row r="23">
@@ -863,14 +855,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="C23">
-        <v>14131</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>0.370216573158447</v>
+        <v>0.0007882226030713657</v>
       </c>
     </row>
     <row r="24">
@@ -881,220 +873,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="C24">
-        <v>19394</v>
+        <v>593</v>
       </c>
       <c r="D24">
-        <v>0.5081013530418881</v>
+        <v>0.06677371480304568</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="C25">
-        <v>17886</v>
+        <v>31006</v>
       </c>
       <c r="D25">
-        <v>0.4685934206717135</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Physical Hand Therapist</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>1083</v>
-      </c>
-      <c r="D26">
-        <v>0.02837340235868644</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Physician Assistant</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>237580</v>
-      </c>
-      <c r="D27">
-        <v>6.224333270892635</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Podiatrist</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>807</v>
-      </c>
-      <c r="D28">
-        <v>0.02114250757475527</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Professional Behavioral Health Counselor</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>359</v>
-      </c>
-      <c r="D29">
-        <v>0.009405402997939457</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Radiography Technologist</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>52</v>
-      </c>
-      <c r="D30">
-        <v>0.001362342495523264</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Registered Dietitian</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>364</v>
-      </c>
-      <c r="D31">
-        <v>0.009536397468662847</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>16</v>
-      </c>
-      <c r="D32">
-        <v>0.0004191823063148504</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>2310</v>
-      </c>
-      <c r="D33">
-        <v>0.06051944547420654</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Surgical Physician Assistant</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>1618</v>
-      </c>
-      <c r="D34">
-        <v>0.04238981072608925</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Uncategorised</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>No matching concept</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>87733</v>
-      </c>
-      <c r="D35">
-        <v>2.298507579995048</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36">
-        <v>102</v>
-      </c>
-      <c r="D36">
-        <v>0.002672287202757171</v>
+        <v>3.491375718690109</v>
       </c>
     </row>
   </sheetData>
